--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T10:02:10-03:00</t>
+    <t>2026-09-25T17:16:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T17:16:20-03:00</t>
+    <t>2026-09-28T11:57:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:57:19-03:00</t>
+    <t>2026-09-30T19:22:44-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2761" uniqueCount="476">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:22:44-03:00</t>
+    <t>2026-10-08T21:08:49-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1171,6 +1171,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.target[classCode="DOC", moodCode="EVN"].id</t>
   </si>
   <si>
@@ -1191,6 +1194,18 @@
   </si>
   <si>
     <t>Referencia a composition alvo</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo.target[x]:targetIdentifier</t>
+  </si>
+  <si>
+    <t>targetIdentifier</t>
+  </si>
+  <si>
+    <t>Target of the relationship</t>
+  </si>
+  <si>
+    <t>The target composition/document of this relationship.</t>
   </si>
   <si>
     <t>Composition.event</t>
@@ -1769,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO73"/>
+  <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.78515625" customWidth="true" bestFit="true"/>
@@ -7734,7 +7749,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>181</v>
+        <v>374</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>370</v>
@@ -7755,13 +7770,13 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -7769,13 +7784,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
@@ -7797,13 +7812,13 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7872,13 +7887,13 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -7886,12 +7901,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7900,7 +7917,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -7909,23 +7926,19 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>312</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O53" t="s" s="2">
         <v>385</v>
       </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7973,13 +7986,13 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
@@ -7991,13 +8004,13 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8005,10 +8018,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8019,7 +8032,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8028,19 +8041,23 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>175</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8088,31 +8105,31 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>176</v>
+        <v>386</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>158</v>
+        <v>391</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8120,10 +8137,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8134,7 +8151,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8146,13 +8163,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>178</v>
+        <v>395</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8203,25 +8220,25 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8235,10 +8252,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8255,19 +8272,19 @@
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8318,7 +8335,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>323</v>
+        <v>182</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8350,10 +8367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8370,23 +8387,21 @@
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8411,11 +8426,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8433,7 +8450,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8445,19 +8462,19 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8465,10 +8482,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8479,7 +8496,7 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -8491,15 +8508,17 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8524,13 +8543,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8548,13 +8565,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8566,10 +8583,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>403</v>
@@ -8594,7 +8611,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8612,7 +8629,7 @@
         <v>406</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8669,7 +8686,7 @@
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8681,13 +8698,13 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>407</v>
+        <v>286</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8695,10 +8712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8718,16 +8735,16 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>312</v>
+        <v>410</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8778,7 +8795,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8790,16 +8807,16 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>410</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>412</v>
+        <v>158</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8824,7 +8841,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8836,13 +8853,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>414</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8893,28 +8910,28 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>176</v>
+        <v>413</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>158</v>
+        <v>416</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8925,10 +8942,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8939,7 +8956,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -8951,13 +8968,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>178</v>
+        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9008,25 +9025,25 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9040,10 +9057,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9060,19 +9077,19 @@
         <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9123,7 +9140,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>182</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9155,46 +9172,42 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>420</v>
+        <v>322</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9242,28 +9255,28 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9274,14 +9287,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9300,7 +9313,7 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>425</v>
@@ -9337,11 +9350,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9359,7 +9374,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9377,10 +9392,10 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>170</v>
+        <v>303</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9391,10 +9406,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9405,7 +9420,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9417,17 +9432,19 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>290</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>293</v>
+        <v>433</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9452,13 +9469,11 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9476,13 +9491,13 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
@@ -9494,24 +9509,24 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>298</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9522,7 +9537,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9534,18 +9549,18 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>405</v>
+        <v>290</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9593,13 +9608,13 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
@@ -9611,24 +9626,24 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>436</v>
+        <v>296</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>78</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9651,16 +9666,16 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>116</v>
+        <v>410</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9710,7 +9725,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9719,7 +9734,7 @@
         <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
@@ -9728,7 +9743,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>441</v>
@@ -9768,7 +9783,7 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>443</v>
@@ -9779,9 +9794,7 @@
       <c r="N69" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="O69" t="s" s="2">
-        <v>445</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9805,11 +9818,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9836,7 +9851,7 @@
         <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>100</v>
@@ -9845,24 +9860,24 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>158</v>
+        <v>446</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9885,19 +9900,19 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9922,11 +9937,11 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -9944,7 +9959,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9962,7 +9977,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>158</v>
@@ -9971,15 +9986,15 @@
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9990,7 +10005,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10002,18 +10017,20 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>405</v>
+        <v>162</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10037,13 +10054,11 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10061,16 +10076,16 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>100</v>
@@ -10082,7 +10097,7 @@
         <v>458</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>459</v>
+        <v>158</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10093,10 +10108,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10107,7 +10122,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10119,20 +10134,18 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10156,13 +10169,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10180,16 +10193,16 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -10198,10 +10211,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>158</v>
+        <v>464</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10212,10 +10225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10226,7 +10239,7 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10238,18 +10251,20 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10273,13 +10288,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10297,16 +10312,16 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
@@ -10315,15 +10330,132 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>470</v>
+        <v>158</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO73" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T21:08:49-03:00</t>
+    <t>2026-10-16T11:47:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-composition.xlsx
+++ b/output/StructureDefinition-br-core-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:47:57-03:00</t>
+    <t>2026-10-19T17:00:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
